--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2325,7 +2325,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2024-10-28</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4495,7 +4495,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6789,7 +6789,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -9703,14 +9703,14 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
         <v>8360000</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>22175</v>
+        <v>22116</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>8360000</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>22175</v>
+        <v>22116</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10889,7 +10889,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11137,7 +11137,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-11</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11757,7 +11757,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2024-06-27</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12935,7 +12935,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13307,7 +13307,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13679,7 +13679,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13803,7 +13803,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13865,7 +13865,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2024-08-11</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14423,7 +14423,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14485,7 +14485,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14609,7 +14609,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14671,7 +14671,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14795,7 +14795,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14857,7 +14857,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14919,7 +14919,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15043,7 +15043,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15353,7 +15353,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15415,7 +15415,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15601,7 +15601,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15849,7 +15849,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15973,7 +15973,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16035,7 +16035,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16097,7 +16097,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16159,7 +16159,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16221,7 +16221,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16283,7 +16283,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16345,7 +16345,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16407,7 +16407,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16469,7 +16469,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16655,7 +16655,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16903,7 +16903,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17337,7 +17337,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17585,7 +17585,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17833,7 +17833,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -17957,7 +17957,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18081,7 +18081,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18143,7 +18143,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18205,7 +18205,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18453,7 +18453,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18577,7 +18577,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19019,7 +19019,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19205,7 +19205,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19267,7 +19267,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19329,7 +19329,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19453,7 +19453,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19887,7 +19887,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20197,7 +20197,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20259,7 +20259,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20383,7 +20383,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20507,7 +20507,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20693,7 +20693,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20941,7 +20941,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21003,7 +21003,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21065,7 +21065,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21189,7 +21189,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21313,7 +21313,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21375,7 +21375,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21499,7 +21499,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21561,7 +21561,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21623,7 +21623,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21685,7 +21685,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21747,7 +21747,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21809,7 +21809,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21871,7 +21871,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21933,7 +21933,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22057,7 +22057,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22119,7 +22119,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22181,7 +22181,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2024-05-27</t>
+          <t>2024-05-28</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22429,7 +22429,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22491,7 +22491,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22553,7 +22553,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22677,7 +22677,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22739,7 +22739,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22801,7 +22801,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22863,7 +22863,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23049,7 +23049,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23173,7 +23173,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23235,7 +23235,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23359,7 +23359,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23421,7 +23421,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23669,7 +23669,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23731,7 +23731,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23793,7 +23793,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -23917,7 +23917,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -23979,7 +23979,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24103,7 +24103,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24165,7 +24165,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24227,7 +24227,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24413,7 +24413,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24537,7 +24537,7 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H386" s="5" t="n">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24723,7 +24723,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -24847,7 +24847,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -24971,7 +24971,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -25033,7 +25033,7 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H394" s="5" t="n">
@@ -25095,7 +25095,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25157,7 +25157,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25219,7 +25219,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25343,7 +25343,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -25467,7 +25467,7 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H401" s="5" t="n">
@@ -25529,7 +25529,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25591,7 +25591,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25653,7 +25653,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -25715,7 +25715,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -25777,7 +25777,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -25839,7 +25839,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -25901,7 +25901,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -25963,7 +25963,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26273,7 +26273,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -26335,7 +26335,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -26397,7 +26397,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26459,7 +26459,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26521,7 +26521,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26583,7 +26583,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26645,7 +26645,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -26707,7 +26707,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -26769,7 +26769,7 @@
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
@@ -26831,7 +26831,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27017,7 +27017,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -27141,7 +27141,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -27203,7 +27203,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
@@ -27327,7 +27327,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H433" s="5" t="n">
@@ -27513,7 +27513,7 @@
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H434" s="5" t="n">
@@ -27575,7 +27575,7 @@
       </c>
       <c r="G435" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H435" s="5" t="n">
@@ -27707,7 +27707,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -27769,7 +27769,7 @@
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
@@ -27831,7 +27831,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -27893,7 +27893,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -27955,7 +27955,7 @@
       </c>
       <c r="G441" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H441" s="5" t="n">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="G442" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H442" s="5" t="n">
@@ -28079,7 +28079,7 @@
       </c>
       <c r="G443" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H443" s="5" t="n">
@@ -28141,7 +28141,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -28203,7 +28203,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -28265,7 +28265,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -28327,7 +28327,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -28389,7 +28389,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -28451,7 +28451,7 @@
       </c>
       <c r="G449" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H449" s="5" t="n">
@@ -28513,7 +28513,7 @@
       </c>
       <c r="G450" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H450" s="5" t="n">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="G451" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H451" s="5" t="n">
@@ -28637,7 +28637,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -28699,7 +28699,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -28761,7 +28761,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -28823,7 +28823,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -28885,7 +28885,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -28947,7 +28947,7 @@
       </c>
       <c r="G457" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H457" s="5" t="n">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="G458" s="3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="H458" s="5" t="n">
@@ -29071,7 +29071,7 @@
       </c>
       <c r="G459" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H459" s="5" t="n">
@@ -29133,7 +29133,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -29257,7 +29257,7 @@
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
@@ -29319,7 +29319,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -29381,7 +29381,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="G465" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H465" s="5" t="n">
@@ -29505,7 +29505,7 @@
       </c>
       <c r="G466" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H466" s="5" t="n">
@@ -29567,7 +29567,7 @@
       </c>
       <c r="G467" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H467" s="5" t="n">
@@ -29629,7 +29629,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -29691,7 +29691,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -29815,7 +29815,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -29877,7 +29877,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -29939,7 +29939,7 @@
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H473" s="5" t="n">
@@ -30001,7 +30001,7 @@
       </c>
       <c r="G474" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H474" s="5" t="n">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H475" s="5" t="n">
@@ -30125,7 +30125,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -30187,7 +30187,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -30249,7 +30249,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -30311,7 +30311,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -30373,7 +30373,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -30435,7 +30435,7 @@
       </c>
       <c r="G481" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H481" s="5" t="n">
@@ -30497,7 +30497,7 @@
       </c>
       <c r="G482" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H482" s="5" t="n">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="G483" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H483" s="5" t="n">
@@ -30621,7 +30621,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -30745,7 +30745,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -30807,7 +30807,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="G489" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H489" s="5" t="n">
@@ -30993,7 +30993,7 @@
       </c>
       <c r="G490" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H490" s="5" t="n">
@@ -31055,7 +31055,7 @@
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H491" s="5" t="n">
@@ -31117,7 +31117,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -31179,7 +31179,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2024-05-27</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -31241,7 +31241,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -31303,7 +31303,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -31427,7 +31427,7 @@
       </c>
       <c r="G497" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H497" s="5" t="n">
@@ -31489,7 +31489,7 @@
       </c>
       <c r="G498" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H498" s="5" t="n">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -31613,7 +31613,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -31675,7 +31675,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -31737,7 +31737,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -31799,7 +31799,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -31861,7 +31861,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -31923,7 +31923,7 @@
       </c>
       <c r="G505" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H505" s="5" t="n">
@@ -31985,7 +31985,7 @@
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H506" s="5" t="n">
@@ -32047,7 +32047,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -32171,7 +32171,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -32233,7 +32233,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -32295,7 +32295,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -32357,7 +32357,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -32419,7 +32419,7 @@
       </c>
       <c r="G513" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H513" s="5" t="n">
@@ -32481,7 +32481,7 @@
       </c>
       <c r="G514" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H514" s="5" t="n">
@@ -32543,7 +32543,7 @@
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H515" s="5" t="n">
@@ -32605,7 +32605,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -32667,7 +32667,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H517" s="5" t="n">
@@ -32729,7 +32729,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
@@ -32791,7 +32791,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -32915,7 +32915,7 @@
       </c>
       <c r="G521" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H521" s="5" t="n">
@@ -32977,7 +32977,7 @@
       </c>
       <c r="G522" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H522" s="5" t="n">
@@ -33039,7 +33039,7 @@
       </c>
       <c r="G523" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H523" s="5" t="n">
@@ -33101,7 +33101,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -33163,7 +33163,7 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
@@ -33225,7 +33225,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -33287,7 +33287,7 @@
       </c>
       <c r="G527" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H527" s="5" t="n">
@@ -33349,7 +33349,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -33411,7 +33411,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -33473,7 +33473,7 @@
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H530" s="5" t="n">
@@ -33535,7 +33535,7 @@
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H531" s="5" t="n">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -33659,7 +33659,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -33721,7 +33721,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -33783,7 +33783,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -33845,7 +33845,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -33907,7 +33907,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -33969,7 +33969,7 @@
       </c>
       <c r="G538" s="3" t="inlineStr">
         <is>
-          <t>2024-05-16</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H538" s="5" t="n">
@@ -34031,7 +34031,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -34093,7 +34093,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -34155,7 +34155,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -34217,7 +34217,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -34279,7 +34279,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -34341,7 +34341,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="G545" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H545" s="5" t="n">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="G546" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H546" s="5" t="n">
@@ -34527,7 +34527,7 @@
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H547" s="5" t="n">
@@ -34589,7 +34589,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -34651,7 +34651,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2024-05-23</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -34775,7 +34775,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -34837,7 +34837,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -34899,7 +34899,7 @@
       </c>
       <c r="G553" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H553" s="5" t="n">
@@ -34961,7 +34961,7 @@
       </c>
       <c r="G554" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H554" s="5" t="n">
@@ -35023,7 +35023,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -35085,7 +35085,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -35147,7 +35147,7 @@
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H557" s="5" t="n">
@@ -35209,7 +35209,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -35271,7 +35271,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -35333,7 +35333,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -35395,7 +35395,7 @@
       </c>
       <c r="G561" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H561" s="5" t="n">
@@ -35457,7 +35457,7 @@
       </c>
       <c r="G562" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H562" s="5" t="n">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -35581,7 +35581,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-23</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -35643,7 +35643,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -35705,7 +35705,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -35767,7 +35767,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -35829,7 +35829,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -35891,7 +35891,7 @@
       </c>
       <c r="G569" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H569" s="5" t="n">
@@ -35953,7 +35953,7 @@
       </c>
       <c r="G570" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H570" s="5" t="n">
@@ -36015,7 +36015,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -36077,7 +36077,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2024-05-19</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -36139,7 +36139,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2024-05-16</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -36201,7 +36201,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -36387,7 +36387,7 @@
           <t>C | 390呎 (1房)
 $880万
 $22,559/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -36395,7 +36395,7 @@
           <t>D | 539呎 (2房)
 $1467万
 $27,219/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -36403,7 +36403,7 @@
           <t>E | 488呎 (2房)
 $1333万
 $27,316/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -36426,7 +36426,7 @@
           <t>A | 783呎 (3房)
 $2031万
 $25,935/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -36434,7 +36434,7 @@
           <t>B | 536呎 (2房)
 $1336万
 $24,924/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -36442,7 +36442,7 @@
           <t>C | 388呎 (1房)
 $836万
 $21,549/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -36450,7 +36450,7 @@
           <t>D | 539呎 (2房)
 $1338万
 $24,827/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -36458,7 +36458,7 @@
           <t>E | 488呎 (2房)
 $1216万
 $24,922/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -36466,7 +36466,7 @@
           <t>F | 555呎 (2房)
 $1447万
 $26,077/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -36481,7 +36481,7 @@
           <t>A | 783呎 (3房)
 $2021万
 $25,808/呎
-(24年-10月-23日)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -36497,7 +36497,7 @@
           <t>C | 388呎 (1房)
 $815万
 $20,995/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -36505,7 +36505,7 @@
           <t>D | 539呎 (2房)
 $1325万
 $24,584/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -36513,7 +36513,7 @@
           <t>E | 488呎 (2房)
 $1263万
 $25,883/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -36536,7 +36536,7 @@
           <t>A | 783呎 (3房)
 $1992万
 $25,434/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -36544,7 +36544,7 @@
           <t>B | 536呎 (2房)
 $1310万
 $24,438/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -36552,7 +36552,7 @@
           <t>C | 388呎 (1房)
 $805万
 $20,747/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -36560,7 +36560,7 @@
           <t>D | 539呎 (2房)
 $1300万
 $24,109/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -36568,7 +36568,7 @@
           <t>E | 488呎 (2房)
 $1210万
 $24,791/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -36576,7 +36576,7 @@
           <t>F | 555呎 (2房)
 $1440万
 $25,941/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -36591,7 +36591,7 @@
           <t>A | 783呎 (3房)
 $1982万
 $25,310/呎
-(24年-10月-08日)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -36607,7 +36607,7 @@
           <t>C | 388呎 (1房)
 $803万
 $20,706/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -36615,7 +36615,7 @@
           <t>D | 539呎 (2房)
 $1287万
 $23,874/呎
-(24年-07月-24日)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -36623,7 +36623,7 @@
           <t>E | 488呎 (2房)
 $1170万
 $23,965/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -36631,7 +36631,7 @@
           <t>F | 555呎 (2房)
 $1426万
 $25,686/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -36646,7 +36646,7 @@
           <t>A | 783呎 (3房)
 $1972万
 $25,186/呎
-(24年-07月-16日)</t>
+(24年-07月-17日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -36662,7 +36662,7 @@
           <t>C | 388呎 (1房)
 $802万
 $20,665/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -36670,7 +36670,7 @@
           <t>D | 539呎 (2房)
 $1274万
 $23,640/呎
-(24年-07月-17日)</t>
+(24年-07月-18日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -36678,7 +36678,7 @@
           <t>E | 488呎 (2房)
 $1158万
 $23,732/呎
-(24年-10月-28日)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -36686,7 +36686,7 @@
           <t>F | 555呎 (2房)
 $1365万
 $24,589/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -36701,7 +36701,7 @@
           <t>A | 783呎 (3房)
 $2010万
 $25,676/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -36717,7 +36717,7 @@
           <t>C | 388呎 (1房)
 $800万
 $20,624/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -36725,7 +36725,7 @@
           <t>D | 539呎 (2房)
 $1262万
 $23,410/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -36733,7 +36733,7 @@
           <t>E | 488呎 (2房)
 $1147万
 $23,500/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -36741,7 +36741,7 @@
           <t>F | 555呎 (2房)
 $1371万
 $24,703/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -36756,7 +36756,7 @@
           <t>A | 783呎 (3房)
 $1953万
 $24,941/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -36764,7 +36764,7 @@
           <t>B | 536呎 (2房)
 $1316万
 $24,547/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -36772,7 +36772,7 @@
           <t>C | 388呎 (1房)
 $799万
 $20,582/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -36780,7 +36780,7 @@
           <t>D | 539呎 (2房)
 $1280万
 $23,746/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -36788,7 +36788,7 @@
           <t>E | 488呎 (2房)
 $1163万
 $23,838/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -36796,7 +36796,7 @@
           <t>F | 555呎 (2房)
 $1344万
 $24,223/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -36811,7 +36811,7 @@
           <t>A | 783呎 (3房)
 $1991万
 $25,425/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -36819,7 +36819,7 @@
           <t>B | 536呎 (2房)
 $1278万
 $23,845/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -36827,7 +36827,7 @@
           <t>C | 388呎 (1房)
 $817万
 $21,046/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -36835,7 +36835,7 @@
           <t>D | 539呎 (2房)
 $1237万
 $22,954/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -36843,7 +36843,7 @@
           <t>E | 488呎 (2房)
 $1152万
 $23,609/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -36851,7 +36851,7 @@
           <t>F | 555呎 (2房)
 $1318万
 $23,755/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -36866,7 +36866,7 @@
           <t>A | 783呎 (3房)
 $1943万
 $24,820/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -36874,7 +36874,7 @@
           <t>B | 536呎 (2房)
 $1278万
 $23,845/呎
-(24年-06月-23日)</t>
+(24年-06月-24日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -36882,7 +36882,7 @@
           <t>C | 388呎 (1房)
 $797万
 $20,544/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -36890,7 +36890,7 @@
           <t>D | 539呎 (2房)
 $1237万
 $22,954/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -36898,7 +36898,7 @@
           <t>E | 488呎 (2房)
 $1125万
 $23,045/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -36906,7 +36906,7 @@
           <t>F | 555呎 (2房)
 $1306万
 $23,524/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -36921,7 +36921,7 @@
           <t>A | 783呎 (3房)
 $1924万
 $24,579/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -36929,7 +36929,7 @@
           <t>B | 536呎 (2房)
 $1266万
 $23,612/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -36937,7 +36937,7 @@
           <t>C | 388呎 (1房)
 $792万
 $20,399/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -36945,7 +36945,7 @@
           <t>D | 539呎 (2房)
 $1255万
 $23,284/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -36953,7 +36953,7 @@
           <t>E | 488呎 (2房)
 $1141万
 $23,375/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -36961,7 +36961,7 @@
           <t>F | 555呎 (2房)
 $1238万
 $22,305/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -36976,7 +36976,7 @@
           <t>A | 783呎 (3房)
 $1962万
 $25,055/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -36992,7 +36992,7 @@
           <t>C | 388呎 (1房)
 $790万
 $20,361/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -37000,7 +37000,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,620/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -37008,7 +37008,7 @@
           <t>E | 488呎 (2房)
 $1115万
 $22,848/呎
-(24年-10月-17日)</t>
+(24年-10月-18日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -37016,7 +37016,7 @@
           <t>F | 555呎 (2房)
 $1244万
 $22,405/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -37031,7 +37031,7 @@
           <t>A | 783呎 (3房)
 $1906万
 $24,340/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -37047,7 +37047,7 @@
           <t>C | 388呎 (1房)
 $808万
 $20,817/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -37055,7 +37055,7 @@
           <t>D | 539呎 (2房)
 $1272万
 $23,607/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -37063,7 +37063,7 @@
           <t>E | 488呎 (2房)
 $1103万
 $22,596/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -37071,7 +37071,7 @@
           <t>F | 555呎 (2房)
 $1211万
 $21,825/呎
-(24年-07月-03日)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
     </row>
@@ -37086,7 +37086,7 @@
           <t>A | 783呎 (3房)
 $1896万
 $24,221/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -37102,7 +37102,7 @@
           <t>C | 388呎 (1房)
 $806万
 $20,773/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -37110,7 +37110,7 @@
           <t>D | 539呎 (2房)
 $1207万
 $22,397/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -37118,7 +37118,7 @@
           <t>E | 488呎 (2房)
 $1124万
 $23,035/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -37126,7 +37126,7 @@
           <t>F | 555呎 (2房)
 $1205万
 $21,717/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -37141,7 +37141,7 @@
           <t>A | 783呎 (3房)
 $1869万
 $23,870/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -37157,7 +37157,7 @@
           <t>C | 388呎 (1房)
 $778万
 $20,041/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -37165,7 +37165,7 @@
           <t>D | 539呎 (2房)
 $1231万
 $22,831/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -37173,7 +37173,7 @@
           <t>E | 488呎 (2房)
 $1119万
 $22,922/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -37181,7 +37181,7 @@
           <t>F | 555呎 (2房)
 $1171万
 $21,095/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -37196,7 +37196,7 @@
           <t>A | 783呎 (3房)
 $1887万
 $24,098/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -37212,7 +37212,7 @@
           <t>C | 388呎 (1房)
 $787万
 $20,289/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -37220,7 +37220,7 @@
           <t>D | 539呎 (2房)
 $1225万
 $22,720/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -37228,7 +37228,7 @@
           <t>E | 488呎 (2房)
 $1087万
 $22,266/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -37236,7 +37236,7 @@
           <t>F | 555呎 (2房)
 $1165万
 $20,993/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -37251,7 +37251,7 @@
           <t>A | 783呎 (3房)
 $1860万
 $23,750/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -37267,7 +37267,7 @@
           <t>C | 388呎 (1房)
 $759万
 $19,570/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -37275,7 +37275,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,609/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -37283,7 +37283,7 @@
           <t>E | 488呎 (2房)
 $1108万
 $22,699/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -37291,7 +37291,7 @@
           <t>F | 555呎 (2房)
 $1188万
 $21,400/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -37306,7 +37306,7 @@
           <t>A | 783呎 (3房)
 $1798万
 $22,959/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -37314,7 +37314,7 @@
           <t>B | 536呎 (2房)
 $1210万
 $22,584/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -37322,7 +37322,7 @@
           <t>C | 388呎 (1房)
 $752万
 $19,379/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -37330,7 +37330,7 @@
           <t>D | 539呎 (2房)
 $1219万
 $22,609/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -37338,7 +37338,7 @@
           <t>E | 488呎 (2房)
 $1108万
 $22,699/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -37346,7 +37346,7 @@
           <t>F | 555呎 (2房)
 $1188万
 $21,400/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -37361,7 +37361,7 @@
           <t>A | 783呎 (3房)
 $1806万
 $23,068/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -37377,7 +37377,7 @@
           <t>C | 388呎 (1房)
 $757万
 $19,521/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -37385,7 +37385,7 @@
           <t>D | 539呎 (2房)
 $1178万
 $21,855/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -37393,7 +37393,7 @@
           <t>E | 488呎 (2房)
 $1097万
 $22,480/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -37401,7 +37401,7 @@
           <t>F | 555呎 (2房)
 $1148万
 $20,686/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -37416,7 +37416,7 @@
           <t>A | 783呎 (3房)
 $1797万
 $22,955/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -37432,7 +37432,7 @@
           <t>C | 388呎 (1房)
 $756万
 $19,482/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -37440,7 +37440,7 @@
           <t>D | 539呎 (2房)
 $1201万
 $22,278/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -37448,7 +37448,7 @@
           <t>E | 488呎 (2房)
 $1066万
 $21,834/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -37456,7 +37456,7 @@
           <t>F | 555呎 (2房)
 $1142万
 $20,584/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -37471,7 +37471,7 @@
           <t>A | 783呎 (3房)
 $1789万
 $22,844/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -37487,7 +37487,7 @@
           <t>C | 388呎 (1房)
 $754万
 $19,446/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -37495,7 +37495,7 @@
           <t>D | 539呎 (2房)
 $1166万
 $21,640/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -37503,7 +37503,7 @@
           <t>E | 488呎 (2房)
 $1060万
 $21,727/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -37511,7 +37511,7 @@
           <t>F | 555呎 (2房)
 $1137万
 $20,483/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -37542,7 +37542,7 @@
           <t>C | 388呎 (1房)
 $735万
 $18,943/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -37550,7 +37550,7 @@
           <t>D | 539呎 (2房)
 $1189万
 $22,059/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -37558,7 +37558,7 @@
           <t>E | 488呎 (2房)
 $1055万
 $21,621/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -37566,7 +37566,7 @@
           <t>F | 555呎 (2房)
 $1131万
 $20,384/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
     </row>
@@ -37597,7 +37597,7 @@
           <t>C | 388呎 (1房)
 $734万
 $18,905/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -37605,7 +37605,7 @@
           <t>D | 539呎 (2房)
 $1155万
 $21,429/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -37613,7 +37613,7 @@
           <t>E | 488呎 (2房)
 $1050万
 $21,516/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -37621,7 +37621,7 @@
           <t>F | 555呎 (2房)
 $1126万
 $20,283/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -37636,7 +37636,7 @@
           <t>A | 740呎 (3房)
 $1934万
 $26,134/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -37644,7 +37644,7 @@
           <t>B | 498呎 (2房)
 $1219万
 $24,474/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -37660,7 +37660,7 @@
           <t>D | 502呎 (2房)
 $1231万
 $24,518/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -37668,7 +37668,7 @@
           <t>E | 450呎 (2房)
 $1120万
 $24,889/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -37676,7 +37676,7 @@
           <t>F | 517呎 (2房)
 $1171万
 $22,646/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -37835,7 +37835,7 @@
           <t>C | 387呎 (1房)
 $856万
 $22,106/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -37843,15 +37843,15 @@
           <t>D | 377呎 (1房)
 $858万
 $22,772/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>E | 377呎 (1房)
+          <t>E | 378呎 (1房)
 $836万
-$22,175/呎
-(24年-05月-27日)</t>
+$22,116/呎
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -37859,7 +37859,7 @@
           <t>F | 525呎 (2房)
 $1402万
 $26,709/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -37874,7 +37874,7 @@
           <t>A | 757呎 (3房)
 $1970万
 $26,026/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -37890,7 +37890,7 @@
           <t>C | 387呎 (1房)
 $799万
 $20,651/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -37898,7 +37898,7 @@
           <t>D | 377呎 (1房)
 $801万
 $21,249/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -37906,7 +37906,7 @@
           <t>E | 378呎 (1房)
 $780万
 $20,638/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -37914,7 +37914,7 @@
           <t>F | 525呎 (2房)
 $1244万
 $23,688/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -37929,7 +37929,7 @@
           <t>A | 757呎 (3房)
 $2046万
 $27,032/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -37937,7 +37937,7 @@
           <t>B | 521呎 (2房)
 $1354万
 $25,983/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -37945,7 +37945,7 @@
           <t>C | 387呎 (1房)
 $798万
 $20,610/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -37953,7 +37953,7 @@
           <t>D | 377呎 (1房)
 $800万
 $21,207/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -37961,7 +37961,7 @@
           <t>E | 377呎 (1房)
 $779万
 $20,653/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -37969,7 +37969,7 @@
           <t>F | 525呎 (2房)
 $1268万
 $24,145/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -37984,7 +37984,7 @@
           <t>A | 757呎 (3房)
 $1960万
 $25,896/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -37992,7 +37992,7 @@
           <t>B | 521呎 (2房)
 $1296万
 $24,871/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -38000,7 +38000,7 @@
           <t>C | 387呎 (1房)
 $807万
 $20,863/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -38008,7 +38008,7 @@
           <t>D | 377呎 (1房)
 $790万
 $20,958/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -38016,7 +38016,7 @@
           <t>E | 377呎 (1房)
 $788万
 $20,907/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -38024,7 +38024,7 @@
           <t>F | 525呎 (2房)
 $1219万
 $23,223/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -38039,7 +38039,7 @@
           <t>A | 757呎 (3房)
 $1895万
 $25,033/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -38047,7 +38047,7 @@
           <t>B | 521呎 (2房)
 $1283万
 $24,628/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -38055,7 +38055,7 @@
           <t>C | 387呎 (1房)
 $787万
 $20,326/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -38063,7 +38063,7 @@
           <t>D | 377呎 (1房)
 $770万
 $20,416/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -38071,7 +38071,7 @@
           <t>E | 377呎 (1房)
 $768万
 $20,369/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -38079,7 +38079,7 @@
           <t>F | 525呎 (2房)
 $1213万
 $23,109/呎
-(24年-06月-24日)</t>
+(24年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -38094,7 +38094,7 @@
           <t>A | 757呎 (3房)
 $1922万
 $25,394/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -38102,7 +38102,7 @@
           <t>B | 521呎 (2房)
 $1271万
 $24,388/呎
-(24年-09月-10日)</t>
+(24年-09月-11日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -38110,7 +38110,7 @@
           <t>C | 387呎 (1房)
 $804万
 $20,780/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -38118,7 +38118,7 @@
           <t>D | 377呎 (1房)
 $768万
 $20,377/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -38126,7 +38126,7 @@
           <t>E | 377呎 (1房)
 $766万
 $20,329/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -38134,7 +38134,7 @@
           <t>F | 525呎 (2房)
 $1207万
 $22,992/呎
-(24年-06月-27日)</t>
+(24年-06月-28日)</t>
         </is>
       </c>
     </row>
@@ -38149,7 +38149,7 @@
           <t>A | 757呎 (3房)
 $1904万
 $25,148/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -38157,7 +38157,7 @@
           <t>B | 521呎 (2房)
 $1258万
 $24,150/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -38165,7 +38165,7 @@
           <t>C | 387呎 (1房)
 $784万
 $20,245/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -38173,7 +38173,7 @@
           <t>D | 377呎 (1房)
 $785万
 $20,833/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -38181,7 +38181,7 @@
           <t>E | 377呎 (1房)
 $765万
 $20,289/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -38189,7 +38189,7 @@
           <t>F | 525呎 (2房)
 $1206万
 $22,981/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -38204,7 +38204,7 @@
           <t>A | 757呎 (3房)
 $1840万
 $24,312/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -38212,7 +38212,7 @@
           <t>B | 521呎 (2房)
 $1276万
 $24,497/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -38220,7 +38220,7 @@
           <t>C | 387呎 (1房)
 $801万
 $20,700/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -38228,7 +38228,7 @@
           <t>D | 377呎 (1房)
 $803万
 $21,289/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -38236,7 +38236,7 @@
           <t>E | 377呎 (1房)
 $763万
 $20,247/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -38244,7 +38244,7 @@
           <t>F | 525呎 (2房)
 $1172万
 $22,324/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -38259,7 +38259,7 @@
           <t>A | 757呎 (3房)
 $1867万
 $24,663/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -38267,7 +38267,7 @@
           <t>B | 521呎 (2房)
 $1234万
 $23,681/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -38275,7 +38275,7 @@
           <t>C | 387呎 (1房)
 $780万
 $20,165/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -38283,7 +38283,7 @@
           <t>D | 377呎 (1房)
 $764万
 $20,255/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -38291,7 +38291,7 @@
           <t>E | 378呎 (1房)
 $780万
 $20,646/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -38299,7 +38299,7 @@
           <t>F | 525呎 (2房)
 $1195万
 $22,754/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -38314,7 +38314,7 @@
           <t>A | 757呎 (3房)
 $1822万
 $24,074/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -38322,7 +38322,7 @@
           <t>B | 521呎 (2房)
 $1234万
 $23,681/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -38330,7 +38330,7 @@
           <t>C | 387呎 (1房)
 $780万
 $20,165/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -38338,7 +38338,7 @@
           <t>D | 377呎 (1房)
 $782万
 $20,748/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -38346,7 +38346,7 @@
           <t>E | 377呎 (1房)
 $799万
 $21,191/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -38354,7 +38354,7 @@
           <t>F | 524呎 (2房)
 $1195万
 $22,798/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -38369,7 +38369,7 @@
           <t>A | 757呎 (3房)
 $1762万
 $23,273/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -38377,7 +38377,7 @@
           <t>B | 521呎 (2房)
 $1252万
 $24,021/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -38385,7 +38385,7 @@
           <t>C | 387呎 (1房)
 $794万
 $20,514/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -38393,7 +38393,7 @@
           <t>D | 377呎 (1房)
 $777万
 $20,607/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -38401,7 +38401,7 @@
           <t>E | 378呎 (1房)
 $757万
 $20,016/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -38409,7 +38409,7 @@
           <t>F | 525呎 (2房)
 $1155万
 $21,994/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -38424,7 +38424,7 @@
           <t>A | 757呎 (3房)
 $1753万
 $23,160/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -38432,7 +38432,7 @@
           <t>B | 521呎 (2房)
 $1216万
 $23,334/呎
-(24年-06月-26日)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -38440,7 +38440,7 @@
           <t>C | 388呎 (1房)
 $774万
 $19,936/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -38448,7 +38448,7 @@
           <t>D | 377呎 (1房)
 $757万
 $20,077/呎
-(24年-07月-02日)</t>
+(24年-07月-03日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -38456,7 +38456,7 @@
           <t>E | 377呎 (1房)
 $755万
 $20,029/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -38464,7 +38464,7 @@
           <t>F | 525呎 (2房)
 $1149万
 $21,884/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -38479,7 +38479,7 @@
           <t>A | 757呎 (3房)
 $1745万
 $23,048/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -38487,7 +38487,7 @@
           <t>B | 521呎 (2房)
 $1210万
 $23,221/呎
-(24年-06月-26日)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -38495,7 +38495,7 @@
           <t>C | 387呎 (1房)
 $772万
 $19,946/呎
-(24年-06月-26日)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -38503,7 +38503,7 @@
           <t>D | 377呎 (1房)
 $774万
 $20,525/呎
-(24年-08月-11日)</t>
+(24年-08月-12日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -38511,7 +38511,7 @@
           <t>E | 377呎 (1房)
 $754万
 $19,989/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -38519,7 +38519,7 @@
           <t>F | 525呎 (2房)
 $1143万
 $21,777/呎
-(24年-06月-25日)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -38534,7 +38534,7 @@
           <t>A | 757呎 (3房)
 $1736万
 $22,935/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -38542,7 +38542,7 @@
           <t>B | 521呎 (2房)
 $1233万
 $23,668/呎
-(24年-07月-10日)</t>
+(24年-07月-11日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -38550,7 +38550,7 @@
           <t>C | 387呎 (1房)
 $789万
 $20,393/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -38558,7 +38558,7 @@
           <t>D | 377呎 (1房)
 $754万
 $19,997/呎
-(24年-08月-18日)</t>
+(24年-08月-19日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -38566,7 +38566,7 @@
           <t>E | 377呎 (1房)
 $752万
 $19,950/呎
-(24年-07月-24日)</t>
+(24年-07月-25日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -38574,7 +38574,7 @@
           <t>F | 525呎 (2房)
 $1138万
 $21,669/呎
-(24年-07月-01日)</t>
+(24年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -38589,7 +38589,7 @@
           <t>A | 757呎 (3房)
 $1728万
 $22,823/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -38597,7 +38597,7 @@
           <t>B | 521呎 (2房)
 $1227万
 $23,555/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -38605,7 +38605,7 @@
           <t>C | 387呎 (1房)
 $761万
 $19,672/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -38613,7 +38613,7 @@
           <t>D | 377呎 (1房)
 $763万
 $20,241/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -38621,7 +38621,7 @@
           <t>E | 377呎 (1房)
 $761万
 $20,194/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -38629,7 +38629,7 @@
           <t>F | 525呎 (2房)
 $1121万
 $21,349/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -38644,7 +38644,7 @@
           <t>A | 757呎 (3房)
 $1761万
 $23,266/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -38652,7 +38652,7 @@
           <t>B | 521呎 (2房)
 $1221万
 $23,440/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -38660,7 +38660,7 @@
           <t>C | 387呎 (1房)
 $752万
 $19,442/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -38668,7 +38668,7 @@
           <t>D | 377呎 (1房)
 $736万
 $19,528/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -38676,7 +38676,7 @@
           <t>E | 377呎 (1房)
 $752万
 $19,955/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -38684,7 +38684,7 @@
           <t>F | 525呎 (2房)
 $1104万
 $21,034/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -38699,7 +38699,7 @@
           <t>A | 757呎 (3房)
 $1711万
 $22,601/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -38707,7 +38707,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,768/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -38715,7 +38715,7 @@
           <t>C | 387呎 (1房)
 $762万
 $19,680/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -38723,7 +38723,7 @@
           <t>D | 377呎 (1房)
 $728万
 $19,297/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -38731,7 +38731,7 @@
           <t>E | 377呎 (1房)
 $726万
 $19,252/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -38739,7 +38739,7 @@
           <t>F | 525呎 (2房)
 $1088万
 $20,726/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -38754,7 +38754,7 @@
           <t>A | 757呎 (3房)
 $1711万
 $22,601/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -38762,7 +38762,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,768/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -38770,7 +38770,7 @@
           <t>C | 388呎 (1房)
 $736万
 $18,974/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -38778,7 +38778,7 @@
           <t>D | 378呎 (1房)
 $738万
 $19,521/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -38786,7 +38786,7 @@
           <t>E | 377呎 (1房)
 $754万
 $19,989/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -38794,7 +38794,7 @@
           <t>F | 524呎 (2房)
 $1104万
 $21,063/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -38809,7 +38809,7 @@
           <t>A | 757呎 (3房)
 $1694万
 $22,383/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -38817,7 +38817,7 @@
           <t>B | 521呎 (2房)
 $1175万
 $22,545/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -38825,7 +38825,7 @@
           <t>C | 387呎 (1房)
 $724万
 $18,705/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -38833,7 +38833,7 @@
           <t>D | 377呎 (1房)
 $726万
 $19,249/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -38841,7 +38841,7 @@
           <t>E | 377呎 (1房)
 $724万
 $19,202/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -38849,7 +38849,7 @@
           <t>F | 525呎 (2房)
 $1056万
 $20,120/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -38864,7 +38864,7 @@
           <t>A | 757呎 (3房)
 $1686万
 $22,273/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -38872,7 +38872,7 @@
           <t>B | 521呎 (2房)
 $1169万
 $22,436/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -38880,7 +38880,7 @@
           <t>C | 387呎 (1房)
 $722万
 $18,669/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -38888,7 +38888,7 @@
           <t>D | 377呎 (1房)
 $724万
 $19,210/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -38896,7 +38896,7 @@
           <t>E | 377呎 (1房)
 $705万
 $18,708/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -38904,7 +38904,7 @@
           <t>F | 525呎 (2房)
 $1051万
 $20,021/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -38919,7 +38919,7 @@
           <t>A | 757呎 (3房)
 $1678万
 $22,165/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -38927,7 +38927,7 @@
           <t>B | 521呎 (2房)
 $1192万
 $22,869/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -38935,7 +38935,7 @@
           <t>C | 387呎 (1房)
 $739万
 $19,088/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -38943,7 +38943,7 @@
           <t>D | 377呎 (1房)
 $706万
 $18,716/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -38951,7 +38951,7 @@
           <t>E | 377呎 (1房)
 $704万
 $18,671/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -38959,7 +38959,7 @@
           <t>F | 525呎 (2房)
 $1071万
 $20,408/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -38974,7 +38974,7 @@
           <t>A | 757呎 (3房)
 $1670万
 $22,058/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -38982,7 +38982,7 @@
           <t>B | 521呎 (2房)
 $1186万
 $22,758/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -38990,7 +38990,7 @@
           <t>C | 387呎 (1房)
 $737万
 $19,049/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -38998,7 +38998,7 @@
           <t>D | 377呎 (1房)
 $704万
 $18,679/呎
-(24年-06月-06日)</t>
+(24年-06月-07日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -39006,7 +39006,7 @@
           <t>E | 377呎 (1房)
 $702万
 $18,634/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -39014,7 +39014,7 @@
           <t>F | 525呎 (2房)
 $1041万
 $19,823/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -39029,7 +39029,7 @@
           <t>A | 757呎 (3房)
 $1702万
 $22,485/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -39037,7 +39037,7 @@
           <t>B | 521呎 (2房)
 $1152万
 $22,107/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -39045,7 +39045,7 @@
           <t>C | 387呎 (1房)
 $718万
 $18,558/呎
-(24年-06月-20日)</t>
+(24年-06月-21日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -39053,7 +39053,7 @@
           <t>D | 377呎 (1房)
 $703万
 $18,642/呎
-(24年-06月-11日)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -39061,7 +39061,7 @@
           <t>E | 377呎 (1房)
 $718万
 $19,050/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -39069,7 +39069,7 @@
           <t>F | 525呎 (2房)
 $1036万
 $19,726/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -39084,7 +39084,7 @@
           <t>A | 716呎 (3房)
 $1769万
 $24,707/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -39092,7 +39092,7 @@
           <t>B | 481呎 (2房)
 $1196万
 $24,871/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -39100,7 +39100,7 @@
           <t>C | 350呎 (1房)
 $753万
 $21,509/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -39108,7 +39108,7 @@
           <t>D | 340呎 (1房)
 $732万
 $21,532/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -39116,7 +39116,7 @@
           <t>E | 340呎 (1房)
 $748万
 $22,003/呎
-(24年-05月-25日)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -39124,7 +39124,7 @@
           <t>F | 487呎 (2房)
 $1140万
 $23,405/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
     </row>
@@ -39282,7 +39282,7 @@
           <t>B | 761呎 (3房)
 $1960万
 $25,761/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
@@ -39290,7 +39290,7 @@
           <t>C | 497呎 (2房)
 $1289万
 $25,932/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -39298,7 +39298,7 @@
           <t>D | 388呎 (1房)
 $863万
 $22,250/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -39306,7 +39306,7 @@
           <t>E | 391呎 (1房)
 $858万
 $21,944/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr"/>
@@ -39322,7 +39322,7 @@
           <t>A | 774呎 (3房)
 $2051万
 $26,497/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -39330,7 +39330,7 @@
           <t>B | 760呎 (3房)
 $1859万
 $24,455/呎
-(24年-06月-03日)</t>
+(24年-06月-04日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -39338,7 +39338,7 @@
           <t>C | 497呎 (2房)
 $1142万
 $22,978/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -39346,7 +39346,7 @@
           <t>D | 388呎 (1房)
 $789万
 $20,330/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -39354,7 +39354,7 @@
           <t>E | 388呎 (1房)
 $808万
 $20,812/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -39362,7 +39362,7 @@
           <t>F | 528呎 (2房)
 $1334万
 $25,263/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -39377,7 +39377,7 @@
           <t>A | 774呎 (3房)
 $2030万
 $26,234/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -39385,7 +39385,7 @@
           <t>B | 760呎 (3房)
 $1849万
 $24,334/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -39393,7 +39393,7 @@
           <t>C | 497呎 (2房)
 $1136万
 $22,865/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -39401,7 +39401,7 @@
           <t>D | 388呎 (1房)
 $787万
 $20,289/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -39409,7 +39409,7 @@
           <t>E | 388呎 (1房)
 $773万
 $19,925/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -39417,7 +39417,7 @@
           <t>F | 528呎 (2房)
 $1321万
 $25,013/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -39432,7 +39432,7 @@
           <t>A | 774呎 (3房)
 $1991万
 $25,720/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -39440,7 +39440,7 @@
           <t>B | 760呎 (3房)
 $1779万
 $23,408/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -39448,7 +39448,7 @@
           <t>C | 497呎 (2房)
 $1147万
 $23,082/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -39456,7 +39456,7 @@
           <t>D | 388呎 (1房)
 $797万
 $20,544/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -39464,7 +39464,7 @@
           <t>E | 388呎 (1房)
 $758万
 $19,526/呎
-(24年-05月-29日)</t>
+(24年-05月-30日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -39472,7 +39472,7 @@
           <t>F | 528呎 (2房)
 $1264万
 $23,939/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
     </row>
@@ -39487,7 +39487,7 @@
           <t>A | 774呎 (3房)
 $1924万
 $24,859/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -39495,7 +39495,7 @@
           <t>B | 760呎 (3房)
 $1813万
 $23,861/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -39503,7 +39503,7 @@
           <t>C | 497呎 (2房)
 $1142万
 $22,970/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -39511,7 +39511,7 @@
           <t>D | 388呎 (1房)
 $796万
 $20,503/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -39519,7 +39519,7 @@
           <t>E | 388呎 (1房)
 $745万
 $19,201/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -39527,7 +39527,7 @@
           <t>F | 528呎 (2房)
 $1252万
 $23,703/呎
-(24年-06月-12日)</t>
+(24年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -39542,7 +39542,7 @@
           <t>A | 774呎 (3房)
 $1961万
 $25,339/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -39550,7 +39550,7 @@
           <t>B | 760呎 (3房)
 $1762万
 $23,178/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -39558,7 +39558,7 @@
           <t>C | 497呎 (2房)
 $1136万
 $22,855/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -39566,7 +39566,7 @@
           <t>D | 388呎 (1房)
 $794万
 $20,461/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -39574,7 +39574,7 @@
           <t>E | 389呎 (1房)
 $752万
 $19,332/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -39582,7 +39582,7 @@
           <t>F | 528呎 (2房)
 $1276万
 $24,161/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -39597,7 +39597,7 @@
           <t>A | 774呎 (3房)
 $1952万
 $25,213/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -39605,7 +39605,7 @@
           <t>B | 760呎 (3房)
 $1796万
 $23,626/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -39613,7 +39613,7 @@
           <t>C | 497呎 (2房)
 $1130万
 $22,744/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -39621,7 +39621,7 @@
           <t>D | 388呎 (1房)
 $792万
 $20,423/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -39629,7 +39629,7 @@
           <t>E | 388呎 (1房)
 $727万
 $18,727/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -39637,7 +39637,7 @@
           <t>F | 528呎 (2房)
 $1239万
 $23,468/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -39652,7 +39652,7 @@
           <t>A | 774呎 (3房)
 $1942万
 $25,087/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -39660,7 +39660,7 @@
           <t>B | 760呎 (3房)
 $1787万
 $23,511/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -39668,7 +39668,7 @@
           <t>C | 497呎 (2房)
 $1125万
 $22,632/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -39676,7 +39676,7 @@
           <t>D | 392呎 (1房)
 $772万
 $19,694/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -39684,7 +39684,7 @@
           <t>E | 388呎 (1房)
 $725万
 $18,691/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -39692,7 +39692,7 @@
           <t>F | 528呎 (2房)
 $1263万
 $23,919/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -39707,7 +39707,7 @@
           <t>A | 774呎 (3房)
 $1849万
 $23,893/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -39715,7 +39715,7 @@
           <t>B | 760呎 (3房)
 $1778万
 $23,393/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -39723,7 +39723,7 @@
           <t>C | 497呎 (2房)
 $1119万
 $22,523/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -39731,7 +39731,7 @@
           <t>D | 388呎 (1房)
 $789万
 $20,343/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -39739,7 +39739,7 @@
           <t>E | 388呎 (1房)
 $724万
 $18,652/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -39747,7 +39747,7 @@
           <t>F | 528呎 (2房)
 $1257万
 $23,801/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -39762,7 +39762,7 @@
           <t>A | 774呎 (3房)
 $1813万
 $23,424/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -39770,7 +39770,7 @@
           <t>B | 760呎 (3房)
 $1736万
 $22,837/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -39778,7 +39778,7 @@
           <t>C | 497呎 (2房)
 $1093万
 $21,986/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -39786,7 +39786,7 @@
           <t>D | 388呎 (1房)
 $770万
 $19,858/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -39794,7 +39794,7 @@
           <t>E | 388呎 (1房)
 $724万
 $18,652/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -39802,7 +39802,7 @@
           <t>F | 528呎 (2房)
 $1232万
 $23,333/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -39817,7 +39817,7 @@
           <t>A | 774呎 (3房)
 $1760万
 $22,742/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -39825,7 +39825,7 @@
           <t>B | 760呎 (3房)
 $1719万
 $22,613/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -39833,7 +39833,7 @@
           <t>C | 497呎 (2房)
 $1082万
 $21,773/呎
-(24年-05月-27日)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -39841,7 +39841,7 @@
           <t>D | 388呎 (1房)
 $784万
 $20,204/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -39849,7 +39849,7 @@
           <t>E | 389呎 (1房)
 $719万
 $18,476/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -39857,7 +39857,7 @@
           <t>F | 528呎 (2房)
 $1168万
 $22,116/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -39872,7 +39872,7 @@
           <t>A | 774呎 (3房)
 $1759万
 $22,729/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -39880,7 +39880,7 @@
           <t>B | 760呎 (3房)
 $1752万
 $23,050/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -39888,7 +39888,7 @@
           <t>C | 497呎 (2房)
 $1103万
 $22,195/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -39896,7 +39896,7 @@
           <t>D | 388呎 (1房)
 $782万
 $20,162/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -39904,7 +39904,7 @@
           <t>E | 388呎 (1房)
 $735万
 $18,938/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -39912,7 +39912,7 @@
           <t>F | 528呎 (2房)
 $1167万
 $22,102/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -39927,7 +39927,7 @@
           <t>A | 774呎 (3房)
 $1716万
 $22,174/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -39935,7 +39935,7 @@
           <t>B | 760呎 (3房)
 $1702万
 $22,391/呎
-(24年-10月-22日)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -39943,7 +39943,7 @@
           <t>C | 497呎 (2房)
 $1098万
 $22,085/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -39951,7 +39951,7 @@
           <t>D | 388呎 (1房)
 $781万
 $20,124/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -39959,7 +39959,7 @@
           <t>E | 388呎 (1房)
 $733万
 $18,897/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -39967,7 +39967,7 @@
           <t>F | 528呎 (2房)
 $1139万
 $21,564/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -39982,7 +39982,7 @@
           <t>A | 774呎 (3房)
 $1635万
 $21,119/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -39990,7 +39990,7 @@
           <t>B | 760呎 (3房)
 $1735万
 $22,824/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -39998,7 +39998,7 @@
           <t>C | 497呎 (2房)
 $1066万
 $21,455/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -40006,7 +40006,7 @@
           <t>D | 388呎 (1房)
 $779万
 $20,085/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -40014,7 +40014,7 @@
           <t>E | 388呎 (1房)
 $714万
 $18,412/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -40022,7 +40022,7 @@
           <t>F | 528呎 (2房)
 $1111万
 $21,036/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40037,7 +40037,7 @@
           <t>A | 774呎 (3房)
 $1634万
 $21,106/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -40045,7 +40045,7 @@
           <t>B | 760呎 (3房)
 $1685万
 $22,171/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -40053,7 +40053,7 @@
           <t>C | 497呎 (2房)
 $1087万
 $21,869/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -40061,7 +40061,7 @@
           <t>D | 388呎 (1房)
 $778万
 $20,046/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -40069,7 +40069,7 @@
           <t>E | 388呎 (1房)
 $730万
 $18,825/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -40077,7 +40077,7 @@
           <t>F | 528呎 (2房)
 $1058万
 $20,036/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -40092,7 +40092,7 @@
           <t>A | 774呎 (3房)
 $1593万
 $20,579/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -40100,7 +40100,7 @@
           <t>B | 760呎 (3房)
 $1677万
 $22,062/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -40108,7 +40108,7 @@
           <t>C | 497呎 (2房)
 $1056万
 $21,243/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -40116,7 +40116,7 @@
           <t>D | 388呎 (1房)
 $758万
 $19,531/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -40124,7 +40124,7 @@
           <t>E | 388呎 (1房)
 $712万
 $18,338/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -40132,7 +40132,7 @@
           <t>F | 528呎 (2房)
 $1061万
 $20,100/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -40147,7 +40147,7 @@
           <t>A | 774呎 (3房)
 $1547万
 $19,988/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -40155,7 +40155,7 @@
           <t>B | 760呎 (3房)
 $1709万
 $22,488/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -40163,7 +40163,7 @@
           <t>C | 497呎 (2房)
 $1051万
 $21,141/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -40171,10 +40171,65 @@
           <t>D | 388呎 (1房)
 $756万
 $19,492/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
+        <is>
+          <t>E | 388呎 (1房)
+$710万
+$18,302/呎
+(24年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="G21" s="22" t="inlineStr">
+        <is>
+          <t>F | 528呎 (2房)
+$1031万
+$19,525/呎
+(24年-05月-21日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 774呎 (3房)
+$1547万
+$19,988/呎
+(24年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 760呎 (3房)
+$1668万
+$21,953/呎
 (24年-05月-22日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 497呎 (2房)
+$1051万
+$21,141/呎
+(24年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 388呎 (1房)
+$756万
+$19,492/呎
+(24年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 388呎 (1房)
 $710万
@@ -40182,67 +40237,12 @@
 (24年-05月-20日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
-        <is>
-          <t>F | 528呎 (2房)
-$1031万
-$19,525/呎
-(24年-05月-20日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B22" s="22" t="inlineStr">
-        <is>
-          <t>A | 774呎 (3房)
-$1547万
-$19,988/呎
-(24年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>B | 760呎 (3房)
-$1668万
-$21,953/呎
-(24年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="D22" s="22" t="inlineStr">
-        <is>
-          <t>C | 497呎 (2房)
-$1051万
-$21,141/呎
-(24年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
-        <is>
-          <t>D | 388呎 (1房)
-$756万
-$19,492/呎
-(24年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>E | 388呎 (1房)
-$710万
-$18,302/呎
-(24年-05月-19日)</t>
-        </is>
-      </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 528呎 (2房)
 $1056万
 $20,000/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40257,7 +40257,7 @@
           <t>A | 774呎 (3房)
 $1569万
 $20,273/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -40265,7 +40265,7 @@
           <t>B | 760呎 (3房)
 $1692万
 $22,268/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -40273,7 +40273,7 @@
           <t>C | 497呎 (2房)
 $1066万
 $21,447/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -40281,7 +40281,7 @@
           <t>D | 388呎 (1房)
 $769万
 $19,830/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -40289,7 +40289,7 @@
           <t>E | 388呎 (1房)
 $705万
 $18,175/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -40297,7 +40297,7 @@
           <t>F | 528呎 (2房)
 $1046万
 $19,803/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -40312,7 +40312,7 @@
           <t>A | 774呎 (3房)
 $1561万
 $20,173/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -40320,7 +40320,7 @@
           <t>B | 760呎 (3房)
 $1684万
 $22,159/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -40328,7 +40328,7 @@
           <t>C | 497呎 (2房)
 $1042万
 $20,960/呎
-(24年-10月-24日)</t>
+(24年-10月-25日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -40336,7 +40336,7 @@
           <t>D | 388呎 (1房)
 $750万
 $19,322/呎
-(24年-11月-04日)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -40344,7 +40344,7 @@
           <t>E | 388呎 (1房)
 $704万
 $18,139/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -40352,7 +40352,7 @@
           <t>F | 528呎 (2房)
 $1040万
 $19,706/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -40367,7 +40367,7 @@
           <t>A | 774呎 (3房)
 $1517万
 $19,594/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -40375,7 +40375,7 @@
           <t>B | 760呎 (3房)
 $1636万
 $21,525/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -40383,7 +40383,7 @@
           <t>C | 497呎 (2房)
 $1030万
 $20,730/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -40391,7 +40391,7 @@
           <t>D | 388呎 (1房)
 $748万
 $19,284/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -40399,7 +40399,7 @@
           <t>E | 388呎 (1房)
 $720万
 $18,544/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -40407,7 +40407,7 @@
           <t>F | 528呎 (2房)
 $1011万
 $19,140/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -40422,7 +40422,7 @@
           <t>A | 774呎 (3房)
 $1509万
 $19,497/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -40430,7 +40430,7 @@
           <t>B | 760呎 (3房)
 $1628万
 $21,418/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -40438,7 +40438,7 @@
           <t>C | 497呎 (2房)
 $1025万
 $20,630/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -40446,7 +40446,7 @@
           <t>D | 388呎 (1房)
 $747万
 $19,245/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -40454,7 +40454,7 @@
           <t>E | 388呎 (1房)
 $718万
 $18,508/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -40462,7 +40462,7 @@
           <t>F | 528呎 (2房)
 $1030万
 $19,509/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -40477,7 +40477,7 @@
           <t>A | 774呎 (3房)
 $1502万
 $19,401/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -40485,7 +40485,7 @@
           <t>B | 760呎 (3房)
 $1630万
 $21,443/呎
-(24年-11月-17日)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -40493,7 +40493,7 @@
           <t>C | 497呎 (2房)
 $1045万
 $21,030/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -40501,7 +40501,7 @@
           <t>D | 388呎 (1房)
 $764万
 $19,678/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -40509,7 +40509,7 @@
           <t>E | 388呎 (1房)
 $700万
 $18,031/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -40517,7 +40517,7 @@
           <t>F | 528呎 (2房)
 $1025万
 $19,413/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -40532,7 +40532,7 @@
           <t>A | 732呎 (3房)
 $1570万
 $21,455/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -40540,7 +40540,7 @@
           <t>B | 719呎 (3房)
 $1742万
 $24,224/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -40548,7 +40548,7 @@
           <t>C | 459呎 (2房)
 $1062万
 $23,126/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -40556,7 +40556,7 @@
           <t>D | 350呎 (1房)
 $793万
 $22,651/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -40564,7 +40564,7 @@
           <t>E | 350呎 (1房)
 $756万
 $21,589/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -40572,7 +40572,7 @@
           <t>F | 490呎 (2房)
 $1068万
 $21,788/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -40731,7 +40731,7 @@
           <t>C | 388呎 (1房)
 $812万
 $20,938/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -40739,7 +40739,7 @@
           <t>D | 377呎 (1房)
 $810万
 $21,475/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -40747,7 +40747,7 @@
           <t>E | 377呎 (1房)
 $794万
 $21,064/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -40755,7 +40755,7 @@
           <t>F | 525呎 (2房)
 $1259万
 $23,983/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -40770,7 +40770,7 @@
           <t>A | 757呎 (3房)
 $1818万
 $24,011/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -40778,7 +40778,7 @@
           <t>B | 520呎 (2房)
 $1267万
 $24,363/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -40786,7 +40786,7 @@
           <t>C | 388呎 (1房)
 $776万
 $20,005/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -40794,7 +40794,7 @@
           <t>D | 377呎 (1房)
 $737万
 $19,557/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -40802,7 +40802,7 @@
           <t>E | 377呎 (1房)
 $759万
 $20,130/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -40810,7 +40810,7 @@
           <t>F | 525呎 (2房)
 $1143万
 $21,771/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -40825,7 +40825,7 @@
           <t>A | 757呎 (3房)
 $1844万
 $24,354/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -40833,7 +40833,7 @@
           <t>B | 520呎 (2房)
 $1254万
 $24,123/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -40841,7 +40841,7 @@
           <t>C | 388呎 (1房)
 $765万
 $19,716/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -40849,7 +40849,7 @@
           <t>D | 377呎 (1房)
 $736万
 $19,517/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -40857,7 +40857,7 @@
           <t>E | 377呎 (1房)
 $757万
 $20,090/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -40865,7 +40865,7 @@
           <t>F | 525呎 (2房)
 $1165万
 $22,192/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -40880,7 +40880,7 @@
           <t>A | 757呎 (3房)
 $1807万
 $23,876/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -40888,7 +40888,7 @@
           <t>B | 520呎 (2房)
 $1230万
 $23,648/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -40896,7 +40896,7 @@
           <t>C | 388呎 (1房)
 $736万
 $18,961/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -40904,7 +40904,7 @@
           <t>D | 377呎 (1房)
 $727万
 $19,286/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -40912,7 +40912,7 @@
           <t>E | 377呎 (1房)
 $748万
 $19,851/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -40920,7 +40920,7 @@
           <t>F | 525呎 (2房)
 $1120万
 $21,343/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -40935,7 +40935,7 @@
           <t>A | 757呎 (3房)
 $1747万
 $23,077/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -40943,7 +40943,7 @@
           <t>B | 520呎 (2房)
 $1218万
 $23,415/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -40951,7 +40951,7 @@
           <t>C | 388呎 (1房)
 $725万
 $18,680/呎
-(24年-05月-30日)</t>
+(24年-05月-31日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -40959,7 +40959,7 @@
           <t>D | 377呎 (1房)
 $726万
 $19,249/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -40967,7 +40967,7 @@
           <t>E | 377呎 (1房)
 $729万
 $19,342/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -40975,7 +40975,7 @@
           <t>F | 525呎 (2房)
 $1142万
 $21,754/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -40990,7 +40990,7 @@
           <t>A | 757呎 (3房)
 $1730万
 $22,848/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -40998,7 +40998,7 @@
           <t>B | 520呎 (2房)
 $1177万
 $22,631/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -41006,7 +41006,7 @@
           <t>C | 388呎 (1房)
 $735万
 $18,938/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -41014,7 +41014,7 @@
           <t>D | 377呎 (1房)
 $742万
 $19,682/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -41022,7 +41022,7 @@
           <t>E | 377呎 (1房)
 $728万
 $19,302/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -41030,7 +41030,7 @@
           <t>F | 525呎 (2房)
 $1136万
 $21,646/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41045,7 +41045,7 @@
           <t>A | 757呎 (3房)
 $1712万
 $22,622/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -41053,7 +41053,7 @@
           <t>B | 520呎 (2房)
 $1194万
 $22,954/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -41061,7 +41061,7 @@
           <t>C | 388呎 (1房)
 $716万
 $18,451/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -41069,7 +41069,7 @@
           <t>D | 377呎 (1房)
 $723万
 $19,172/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -41077,7 +41077,7 @@
           <t>E | 377呎 (1房)
 $726万
 $19,265/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -41085,7 +41085,7 @@
           <t>F | 525呎 (2房)
 $1082万
 $20,615/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -41100,7 +41100,7 @@
           <t>A | 757呎 (3房)
 $1696万
 $22,398/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -41108,7 +41108,7 @@
           <t>B | 520呎 (2房)
 $1182万
 $22,725/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -41116,7 +41116,7 @@
           <t>C | 388呎 (1房)
 $714万
 $18,415/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -41124,7 +41124,7 @@
           <t>D | 377呎 (1房)
 $739万
 $19,602/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -41132,7 +41132,7 @@
           <t>E | 377呎 (1房)
 $743万
 $19,698/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -41140,7 +41140,7 @@
           <t>F | 525呎 (2房)
 $1077万
 $20,512/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -41155,7 +41155,7 @@
           <t>A | 757呎 (3房)
 $1720万
 $22,716/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -41163,10 +41163,65 @@
           <t>B | 520呎 (2房)
 $1142万
 $21,965/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 388呎 (1房)
+$713万
+$18,376/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 377呎 (1房)
+$720万
+$19,098/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 377呎 (1房)
+$723万
+$19,188/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 525呎 (2房)
+$1072万
+$20,411/呎
+(24年-05月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 757呎 (3房)
+$1638万
+$21,635/呎
+(24年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 520呎 (2房)
+$1170万
+$22,500/呎
+(24年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 388呎 (1房)
 $713万
@@ -41174,67 +41229,12 @@
 (24年-05月-22日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 377呎 (1房)
 $720万
 $19,098/呎
-(24年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>E | 377呎 (1房)
-$723万
-$19,188/呎
-(24年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="inlineStr">
-        <is>
-          <t>F | 525呎 (2房)
-$1072万
-$20,411/呎
-(24年-05月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>A | 757呎 (3房)
-$1638万
-$21,635/呎
-(24年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 520呎 (2房)
-$1170万
-$22,500/呎
-(24年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>C | 388呎 (1房)
-$713万
-$18,376/呎
-(24年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>D | 377呎 (1房)
-$720万
-$19,098/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -41242,7 +41242,7 @@
           <t>E | 377呎 (1房)
 $741万
 $19,655/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -41250,7 +41250,7 @@
           <t>F | 525呎 (2房)
 $1098万
 $20,909/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -41265,7 +41265,7 @@
           <t>A | 757呎 (3房)
 $1622万
 $21,421/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -41273,7 +41273,7 @@
           <t>B | 520呎 (2房)
 $1131万
 $21,748/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -41281,7 +41281,7 @@
           <t>C | 388呎 (1房)
 $725万
 $18,693/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -41289,7 +41289,7 @@
           <t>D | 377呎 (1房)
 $732万
 $19,430/呎
-(24年-05月-26日)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -41297,7 +41297,7 @@
           <t>E | 378呎 (1房)
 $736万
 $19,468/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -41305,7 +41305,7 @@
           <t>F | 525呎 (2房)
 $1087万
 $20,703/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41320,7 +41320,7 @@
           <t>A | 757呎 (3房)
 $1614万
 $21,314/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -41328,7 +41328,7 @@
           <t>B | 520呎 (2房)
 $1153万
 $22,165/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -41336,7 +41336,7 @@
           <t>C | 388呎 (1房)
 $724万
 $18,657/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -41344,7 +41344,7 @@
           <t>D | 377呎 (1房)
 $731万
 $19,390/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -41352,7 +41352,7 @@
           <t>E | 377呎 (1房)
 $717万
 $19,019/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -41360,7 +41360,7 @@
           <t>F | 525呎 (2房)
 $1081万
 $20,598/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41375,7 +41375,7 @@
           <t>A | 757呎 (3房)
 $1645万
 $21,725/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -41383,7 +41383,7 @@
           <t>B | 520呎 (2房)
 $1120万
 $21,533/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -41391,7 +41391,7 @@
           <t>C | 388呎 (1房)
 $705万
 $18,178/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -41399,7 +41399,7 @@
           <t>D | 377呎 (1房)
 $712万
 $18,891/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -41407,7 +41407,7 @@
           <t>E | 377呎 (1房)
 $716万
 $18,981/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -41415,7 +41415,7 @@
           <t>F | 525呎 (2房)
 $1050万
 $20,008/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41430,7 +41430,7 @@
           <t>A | 757呎 (3房)
 $1636万
 $21,618/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -41438,7 +41438,7 @@
           <t>B | 520呎 (2房)
 $1114万
 $21,425/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -41446,7 +41446,7 @@
           <t>C | 388呎 (1房)
 $721万
 $18,582/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -41454,7 +41454,7 @@
           <t>D | 377呎 (1房)
 $728万
 $19,310/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -41462,7 +41462,7 @@
           <t>E | 377呎 (1房)
 $732万
 $19,406/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -41470,7 +41470,7 @@
           <t>F | 525呎 (2房)
 $1071万
 $20,394/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -41485,7 +41485,7 @@
           <t>A | 757呎 (3房)
 $1628万
 $21,510/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -41493,7 +41493,7 @@
           <t>B | 520呎 (2房)
 $1136万
 $21,837/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -41501,7 +41501,7 @@
           <t>C | 388呎 (1房)
 $702万
 $18,103/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -41509,7 +41509,7 @@
           <t>D | 377呎 (1房)
 $709万
 $18,814/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -41517,7 +41517,7 @@
           <t>E | 377呎 (1房)
 $713万
 $18,905/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -41525,7 +41525,7 @@
           <t>F | 524呎 (2房)
 $1040万
 $19,847/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -41540,7 +41540,7 @@
           <t>A | 757呎 (3房)
 $1620万
 $21,403/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -41548,7 +41548,7 @@
           <t>B | 520呎 (2房)
 $1130万
 $21,729/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -41556,7 +41556,7 @@
           <t>C | 388呎 (1房)
 $701万
 $18,067/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -41564,7 +41564,7 @@
           <t>D | 377呎 (1房)
 $708万
 $18,777/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -41572,7 +41572,7 @@
           <t>E | 377呎 (1房)
 $729万
 $19,326/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -41580,7 +41580,7 @@
           <t>F | 525呎 (2房)
 $1060万
 $20,192/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -41595,7 +41595,7 @@
           <t>A | 757呎 (3房)
 $1612万
 $21,297/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -41603,7 +41603,7 @@
           <t>B | 520呎 (2房)
 $1124万
 $21,621/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -41611,7 +41611,7 @@
           <t>C | 388呎 (1房)
 $700万
 $18,031/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -41619,7 +41619,7 @@
           <t>D | 377呎 (1房)
 $724万
 $19,196/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -41627,7 +41627,7 @@
           <t>E | 377呎 (1房)
 $710万
 $18,830/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -41635,7 +41635,7 @@
           <t>F | 525呎 (2房)
 $1055万
 $20,091/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -41650,7 +41650,7 @@
           <t>A | 757呎 (3房)
 $1612万
 $21,297/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -41658,7 +41658,7 @@
           <t>B | 520呎 (2房)
 $1098万
 $21,106/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -41666,7 +41666,7 @@
           <t>C | 388呎 (1房)
 $734万
 $18,912/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -41674,7 +41674,7 @@
           <t>D | 377呎 (1房)
 $741万
 $19,655/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -41682,7 +41682,7 @@
           <t>E | 377呎 (1房)
 $710万
 $18,830/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -41690,7 +41690,7 @@
           <t>F | 525呎 (2房)
 $1030万
 $19,613/呎
-(24年-05月-16日)</t>
+(24年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -41705,7 +41705,7 @@
           <t>A | 757呎 (3房)
 $1558万
 $20,584/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -41713,7 +41713,7 @@
           <t>B | 520呎 (2房)
 $1087万
 $20,898/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -41721,7 +41721,7 @@
           <t>C | 388呎 (1房)
 $695万
 $17,907/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -41729,7 +41729,7 @@
           <t>D | 377呎 (1房)
 $719万
 $19,064/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -41737,7 +41737,7 @@
           <t>E | 377呎 (1房)
 $722万
 $19,156/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -41745,7 +41745,7 @@
           <t>F | 525呎 (2房)
 $1020万
 $19,419/呎
-(24年-05月-21日)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -41760,7 +41760,7 @@
           <t>A | 757呎 (3房)
 $1550万
 $20,481/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -41768,7 +41768,7 @@
           <t>B | 520呎 (2房)
 $1108万
 $21,302/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -41776,7 +41776,7 @@
           <t>C | 388呎 (1房)
 $710万
 $18,307/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -41784,7 +41784,7 @@
           <t>D | 377呎 (1房)
 $717万
 $19,027/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -41792,7 +41792,7 @@
           <t>E | 377呎 (1房)
 $721万
 $19,117/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -41800,7 +41800,7 @@
           <t>F | 525呎 (2房)
 $1039万
 $19,794/呎
-(24年-05月-23日)</t>
+(24年-05月-24日)</t>
         </is>
       </c>
     </row>
@@ -41815,7 +41815,7 @@
           <t>A | 757呎 (3房)
 $1543万
 $20,379/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -41823,7 +41823,7 @@
           <t>B | 520呎 (2房)
 $1102万
 $21,196/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -41831,7 +41831,7 @@
           <t>C | 388呎 (1房)
 $709万
 $18,271/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -41839,7 +41839,7 @@
           <t>D | 377呎 (1房)
 $699万
 $18,538/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -41847,7 +41847,7 @@
           <t>E | 377呎 (1房)
 $702万
 $18,626/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -41855,7 +41855,7 @@
           <t>F | 525呎 (2房)
 $1009万
 $19,227/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41870,7 +41870,7 @@
           <t>A | 757呎 (3房)
 $1535万
 $20,277/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -41878,7 +41878,7 @@
           <t>B | 520呎 (2房)
 $1097万
 $21,088/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -41886,7 +41886,7 @@
           <t>C | 388呎 (1房)
 $691万
 $17,799/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -41894,7 +41894,7 @@
           <t>D | 377呎 (1房)
 $698万
 $18,501/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -41902,7 +41902,7 @@
           <t>E | 377呎 (1房)
 $701万
 $18,589/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -41910,7 +41910,7 @@
           <t>F | 525呎 (2房)
 $1004万
 $19,131/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -41925,7 +41925,7 @@
           <t>A | 757呎 (3房)
 $1565万
 $20,670/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -41933,7 +41933,7 @@
           <t>B | 520呎 (2房)
 $1065万
 $20,485/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -41941,7 +41941,7 @@
           <t>C | 388呎 (1房)
 $706万
 $18,183/呎
-(24年-05月-20日)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -41949,7 +41949,7 @@
           <t>D | 377呎 (1房)
 $696万
 $18,464/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -41957,7 +41957,7 @@
           <t>E | 377呎 (1房)
 $699万
 $18,552/呎
-(24年-05月-22日)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -41965,7 +41965,7 @@
           <t>F | 525呎 (2房)
 $1024万
 $19,501/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -41980,7 +41980,7 @@
           <t>A | 716呎 (3房)
 $1627万
 $22,722/呎
-(24年-05月-13日)</t>
+(24年-05月-14日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -41988,7 +41988,7 @@
           <t>B | 480呎 (2房)
 $1107万
 $23,058/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -41996,7 +41996,7 @@
           <t>C | 350呎 (1房)
 $736万
 $21,029/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -42004,7 +42004,7 @@
           <t>D | 340呎 (1房)
 $742万
 $21,812/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -42012,7 +42012,7 @@
           <t>E | 340呎 (1房)
 $746万
 $21,935/呎
-(24年-05月-19日)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -42020,7 +42020,7 @@
           <t>F | 487呎 (2房)
 $1080万
 $22,181/呎
-(24年-05月-15日)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -25954,7 +25954,7 @@
         </is>
       </c>
       <c r="E409" s="4" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>7195000</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>18544</v>
+        <v>18496</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>7195000</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>18544</v>
+        <v>18496</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -40396,9 +40396,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>E | 388呎 (1房)
+          <t>E | 389呎 (1房)
 $720万
-$18,544/呎
+$18,496/呎
 (24年-05月-23日)</t>
         </is>
       </c>

--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>11651000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>20993</v>
+        <v>21031</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>11651000</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>20993</v>
+        <v>21031</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>7804000</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>20165</v>
+        <v>20113</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>7804000</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>20165</v>
+        <v>20113</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="E312" s="4" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>12515000</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>23703</v>
+        <v>23748</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>12515000</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>23703</v>
+        <v>23748</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         </is>
       </c>
       <c r="E480" s="4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>7234000</v>
       </c>
       <c r="I480" s="5" t="n">
-        <v>19188</v>
+        <v>19138</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>7234000</v>
       </c>
       <c r="L480" s="5" t="n">
-        <v>19188</v>
+        <v>19138</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
@@ -37233,9 +37233,9 @@
       </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>F | 555呎 (2房)
+          <t>F | 554呎 (2房)
 $1165万
-$20,993/呎
+$21,031/呎
 (24年-05月-27日)</t>
         </is>
       </c>
@@ -38272,9 +38272,9 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>C | 387呎 (1房)
+          <t>C | 388呎 (1房)
 $780万
-$20,165/呎
+$20,113/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -39524,9 +39524,9 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>F | 528呎 (2房)
+          <t>F | 527呎 (2房)
 $1252万
-$23,703/呎
+$23,748/呎
 (24年-06月-13日)</t>
         </is>
       </c>
@@ -41184,9 +41184,9 @@
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>E | 377呎 (1房)
+          <t>E | 378呎 (1房)
 $723万
-$19,188/呎
+$19,138/呎
 (24年-05月-23日)</t>
         </is>
       </c>

--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -34828,7 +34828,7 @@
         </is>
       </c>
       <c r="E552" s="4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>7022000</v>
       </c>
       <c r="I552" s="5" t="n">
-        <v>18626</v>
+        <v>18577</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>7022000</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>18626</v>
+        <v>18577</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
@@ -41844,9 +41844,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>E | 377呎 (1房)
+          <t>E | 378呎 (1房)
 $702万
-$18,626/呎
+$18,577/呎
 (24年-05月-23日)</t>
         </is>
       </c>

--- a/files/九龙-何文田-朗贤峰第IIB期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIB期.xlsx
@@ -13794,7 +13794,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>7569000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>20077</v>
+        <v>20024</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>7569000</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>20077</v>
+        <v>20024</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -38445,9 +38445,9 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>D | 377呎 (1房)
+          <t>D | 378呎 (1房)
 $757万
-$20,077/呎
+$20,024/呎
 (24年-07月-03日)</t>
         </is>
       </c>
